--- a/光伏配储项目/电价数据/2026/陆丰站.xlsx
+++ b/光伏配储项目/电价数据/2026/陆丰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.60139</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80247</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6772100000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60952</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.59026</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.58988</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42096</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43517</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5191399999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.20693</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.22179</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.18563</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20952</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06334000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.16089</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23151</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.95425</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.23063</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.5398200000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.55565</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59892</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7250800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.20706</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.72362</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65367</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.92571</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53003</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.26897</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.3781</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.13818</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.2308</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34194</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.50111</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5060899999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.74564</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7971900000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.30385</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12872</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86388</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79303</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7529400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51414</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46395</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42356</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6984199999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.73835</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8602000000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9003099999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48787</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5055299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.66899</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.53489</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.63142</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5091100000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.86493</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07933</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.59017</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.94169</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8955</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5668200000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.85321</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.26668</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.06126</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58988</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.54014</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85698</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60285</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7643099999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8266699999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.20487</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.75516</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15738</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87162</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.25635</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16092</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.31982</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.1022</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.14561</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70448</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.03598</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89144</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.04589</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9510299999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.07247</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87505</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81616</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8355199999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44561</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33425</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.19038</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24358</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15452</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.56474</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.59368</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.59996</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.67491</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.64373</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.91547</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.60802</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.71294</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.78437</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86937</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52139</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52498</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7739</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7247100000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6441699999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63934</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.59712</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50437</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5122899999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57798</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61283</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5831499999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.22672</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.60848</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.72863</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57974</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71475</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7158300000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.8478</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59729</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45619</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54228</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.59905</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7276900000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8631599999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6945</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5797899999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5176900000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64919</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34153</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49067</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.63149</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.50561</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48432</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.96128</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.58817</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49024</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.63398</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53355</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.65201</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5073799999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.70117</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5478200000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.51312</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50208</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30758</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04127</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.25256</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.24306</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.24059</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.20222</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24854</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22535</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08794</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.16033</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.32871</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.20362</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.07786</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.21504</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.25586</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.23684</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10362</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04409</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20851</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19422</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.21098</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.02846</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06265999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06087</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32246</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.29753</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78487</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8709</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.58711</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.49671</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.55662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.64536</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86725</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45912</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.48775</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.68162</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.44002</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8301799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27774</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5736100000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.47323</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33374</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1933</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.25376</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24656</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28021</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.38806</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.25165</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.79848</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.36822</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.06817</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.64461</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7331299999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.59834</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.45772</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46384</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2183</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24332</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26059</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25346</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24409</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.65423</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.2679</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27299</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.21303</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.22761</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.22285</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.20419</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25112</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.19613</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.19676</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.07795000000000001</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.07862999999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24149</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.25302</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15118</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.21682</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24336</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24741</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22426</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22581</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24158</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24307</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22331</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24088</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22941</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24337</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30415</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32383</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43308</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.21627</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7397699999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.43427</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.54434</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5234099999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.49205</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5621900000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48115</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.81825</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5532100000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.52338</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.49209</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.48985</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.52213</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46011</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.53896</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.44641</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6792100000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.50668</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.49893</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.46104</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.74033</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.44274</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48923</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22138</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.12241</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24121</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.23791</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24023</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21155</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26384</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.23698</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25194</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.22837</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.21743</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26277</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.22219</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32964</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.10957</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6391100000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7972400000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.46572</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.47507</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.59565</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5516</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69135</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6487999999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.71704</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84393</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.6487200000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.53454</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.51749</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.43582</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.32956</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4961</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.53303</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.59824</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.61182</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43547</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6838500000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8613500000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.44795</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.57831</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.43114</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75419</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60603</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6525299999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.36755</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.12433</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.50188</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.01927</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.26979</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28278</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.24379</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.24379</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.25608</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23272</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.22811</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.12435</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.11574</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.11493</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.22833</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.10858</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.24891</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.22725</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.10932</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.21494</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22085</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24419</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.21772</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.22467</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.10573</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.22815</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.10526</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.08856</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.22734</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.20532</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.07964</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.10995</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24441</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.17691</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25382</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.23705</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22247</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22117</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.26482</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.13878</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23084</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.22725</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.09439</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.23809</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.24684</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.12447</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.08749</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.09659999999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.09659000000000001</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23313</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.08566</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.09512000000000001</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.08755</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.08746999999999999</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.09911</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.06325</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.10605</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14041</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01616</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04086</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00123</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03861999999999999</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02319</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03645</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19915</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27738</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.09769</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29639</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.50844</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.18918</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23172</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22834</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.09902</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22367</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.20946</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.06526</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.09276000000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.07068000000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.11886</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.12504</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.13636</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.09242</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.23966</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.53646</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8666900000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8593099999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10534</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.08759</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27518</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18057</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.16941</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00121</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00073</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06683</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47361</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.05087</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.64878</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5390499999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.0518</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.54865</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.71493</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.82986</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82808</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83236</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93025</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5371699999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.5925499999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5452400000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33142</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.21467</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26134</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.24758</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.22672</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.09877</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.52849</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.46882</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.31743</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.45782</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.69064</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.45989</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.5196000000000001</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47281</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.6119600000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84472</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.04212</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.53327</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.56868</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.9500700000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8816900000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5128400000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6307699999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.47195</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.21993</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33662</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43045</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5019400000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5736100000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.17501</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.9652500000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.63374</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.82728</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6234700000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.56843</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7706799999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.71765</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87895</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.78585</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.70633</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45813</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3411</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.42333</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.71114</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21006</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.5028899999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44162</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.7032999999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.46082</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.42778</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.62758</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.49635</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.61878</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.47462</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3467</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.88006</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.51739</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.48177</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.48367</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.56008</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.46529</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.44712</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34948</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17589</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14556</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19837</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14372</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12081</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22482</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14414</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19095</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22655</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15422</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.13952</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.5112300000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37723</v>
       </c>
     </row>
   </sheetData>
